--- a/Code Real/data/4_Data_Clusterized/1_Klaster_Umum/2_Hasil_Klasterisasi/Cluster_Profile_Weighted_K-9.xlsx
+++ b/Code Real/data/4_Data_Clusterized/1_Klaster_Umum/2_Hasil_Klasterisasi/Cluster_Profile_Weighted_K-9.xlsx
@@ -493,13 +493,13 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9421431580361233</v>
+        <v>0.9421431580361235</v>
       </c>
       <c r="D2" t="n">
-        <v>0.49422911611497</v>
+        <v>0.4942291161149697</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9199503262763585</v>
+        <v>0.9199503262763591</v>
       </c>
       <c r="F2" t="n">
         <v>1.150102123311794</v>
@@ -534,7 +534,7 @@
         <v>0.03806331084122391</v>
       </c>
       <c r="E3" t="n">
-        <v>0.169494994400186</v>
+        <v>0.1694949944001861</v>
       </c>
       <c r="F3" t="n">
         <v>0.3553074520974004</v>
@@ -569,7 +569,7 @@
         <v>-0.5804876807739962</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4907174686003765</v>
+        <v>-0.4907174686003763</v>
       </c>
       <c r="F4" t="n">
         <v>-0.449468799726305</v>
@@ -584,7 +584,7 @@
         <v>0.02158091381932707</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.06572601623560417</v>
+        <v>-0.06572601623560415</v>
       </c>
       <c r="K4" t="n">
         <v>-0.1702106043598505</v>
@@ -598,10 +598,10 @@
         <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3272178809332086</v>
+        <v>-0.3272178809332085</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1212065832040071</v>
+        <v>-0.1212065832040072</v>
       </c>
       <c r="E5" t="n">
         <v>1.214824121165764</v>
@@ -619,7 +619,7 @@
         <v>-0.1891480179719353</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9189487600316204</v>
+        <v>0.9189487600316207</v>
       </c>
       <c r="K5" t="n">
         <v>0.08268951923459689</v>
@@ -633,7 +633,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1082527419019811</v>
+        <v>0.108252741901981</v>
       </c>
       <c r="D6" t="n">
         <v>0.5957771839711918</v>
@@ -674,7 +674,7 @@
         <v>9.092892212194817</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3371928562278511</v>
+        <v>-0.3371928562278509</v>
       </c>
       <c r="F7" t="n">
         <v>-0.2445344624632857</v>
@@ -703,13 +703,13 @@
         <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03861291130067513</v>
+        <v>0.03861291130067528</v>
       </c>
       <c r="D8" t="n">
         <v>-0.3929376163931226</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4104213739000366</v>
+        <v>-0.4104213739000364</v>
       </c>
       <c r="F8" t="n">
         <v>0.4631874040692169</v>
@@ -721,13 +721,13 @@
         <v>-0.07669649888473706</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4065682463613468</v>
+        <v>0.4065682463613469</v>
       </c>
       <c r="J8" t="n">
         <v>-0.2709393764064</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.09338959289312078</v>
+        <v>-0.09338959289312075</v>
       </c>
     </row>
     <row r="9">
@@ -738,16 +738,16 @@
         <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.3249162130127295</v>
+        <v>-0.3249162130127294</v>
       </c>
       <c r="D9" t="n">
         <v>0.8864982598566544</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01441144991658021</v>
+        <v>0.01441144991658035</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0288972569541634</v>
+        <v>-0.02889725695416339</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3762607813778516</v>
@@ -759,10 +759,10 @@
         <v>-0.1215935143795131</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08669144663621899</v>
+        <v>0.08669144663621903</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1226989775781027</v>
+        <v>0.1226989775781028</v>
       </c>
     </row>
     <row r="10">
@@ -779,7 +779,7 @@
         <v>1.110098128925304</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1479689519646148</v>
+        <v>-0.1479689519646147</v>
       </c>
       <c r="F10" t="n">
         <v>9.204398684570972</v>
